--- a/Assessment Questions/AIE/ADS-114/Gen AI and Agentic AI Essentials/Transformers & LLMs/Transformers & LLMs.xlsx
+++ b/Assessment Questions/AIE/ADS-114/Gen AI and Agentic AI Essentials/Transformers & LLMs/Transformers & LLMs.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformers_LLMs_Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>Type</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -447,6 +452,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -477,6 +487,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -507,6 +522,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -537,6 +557,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -552,6 +577,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -582,6 +612,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -597,6 +632,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -627,6 +667,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -642,6 +687,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -657,6 +707,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -687,6 +742,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -702,6 +762,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -713,6 +778,11 @@
         </is>
       </c>
       <c r="C20" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Practical</t>
         </is>
